--- a/data/trans_orig/IMC_inf_MED_R3-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IMC_inf_MED_R3-Clase-trans_orig.xlsx
@@ -545,7 +545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido en 2012 (tasa de respuesta: 70,03%)</t>
+          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido en 2012 (tasa de respuesta: 83,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,61 +735,61 @@
         <v>12529</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>7867</v>
+        <v>7517</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>18009</v>
+        <v>18162</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.2179445029921938</v>
+        <v>0.1807631831154169</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.1368535301956118</v>
+        <v>0.1084565238063475</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.3132846658238065</v>
+        <v>0.2620394629233457</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>14904</v>
+        <v>16162</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>10078</v>
+        <v>11290</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>21658</v>
+        <v>23550</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.2234495124374375</v>
+        <v>0.2118208762012205</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.1511004388910385</v>
+        <v>0.1479750826385922</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.3247031324986395</v>
+        <v>0.3086599014147073</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>27433</v>
+        <v>28690</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>20513</v>
+        <v>21392</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>35260</v>
+        <v>37343</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.220901240419376</v>
+        <v>0.1970372549001246</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.16517993308157</v>
+        <v>0.146917312123732</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.2839314080592364</v>
+        <v>0.2564602520745066</v>
       </c>
     </row>
     <row r="5">
@@ -800,67 +800,67 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>44957</v>
+        <v>56781</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>39477</v>
+        <v>51148</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>49619</v>
+        <v>61793</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.7820554970078062</v>
+        <v>0.8192368168845831</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.6867153341761936</v>
+        <v>0.7379605370766542</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.8631464698043884</v>
+        <v>0.8915434761936525</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>51796</v>
+        <v>60136</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>45042</v>
+        <v>52748</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>56622</v>
+        <v>65008</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.7765504875625625</v>
+        <v>0.7881791237987795</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.6752968675013606</v>
+        <v>0.6913400985852921</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.8488995611089617</v>
+        <v>0.8520249173614076</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>138</v>
+        <v>168</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>96753</v>
+        <v>116918</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>88926</v>
+        <v>108265</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>103673</v>
+        <v>124216</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.779098759580624</v>
+        <v>0.8029627450998753</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.7160685919407632</v>
+        <v>0.7435397479254934</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.8348200669184295</v>
+        <v>0.853082687876268</v>
       </c>
     </row>
     <row r="6">
@@ -871,16 +871,16 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>57486</v>
+        <v>69310</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>57486</v>
+        <v>69310</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>57486</v>
+        <v>69310</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
@@ -892,16 +892,16 @@
         <v>1</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>66700</v>
+        <v>76298</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>66700</v>
+        <v>76298</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>66700</v>
+        <v>76298</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>1</v>
@@ -913,16 +913,16 @@
         <v>1</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>178</v>
+        <v>210</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>124186</v>
+        <v>145608</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>124186</v>
+        <v>145608</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>124186</v>
+        <v>145608</v>
       </c>
       <c r="U6" s="6" t="n">
         <v>1</v>
@@ -946,25 +946,25 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>18003</v>
+        <v>18781</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>11921</v>
+        <v>12858</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>23736</v>
+        <v>25103</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.2621230979153835</v>
+        <v>0.234085820616258</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.1735657381494902</v>
+        <v>0.1602659861339404</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.3455986163287468</v>
+        <v>0.3128820712657818</v>
       </c>
       <c r="J7" s="5" t="n">
         <v>19</v>
@@ -973,40 +973,40 @@
         <v>13343</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>8573</v>
+        <v>8253</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>19830</v>
+        <v>19549</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.1894033430051109</v>
+        <v>0.1720960917390693</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.1216931525203855</v>
+        <v>0.1064535645812061</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.281488771258194</v>
+        <v>0.2521412405042381</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>31346</v>
+        <v>32123</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>24063</v>
+        <v>24926</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>39773</v>
+        <v>41819</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.2253023649226604</v>
+        <v>0.2036213705325387</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.1729542293217687</v>
+        <v>0.1579996178930277</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.2858724410918863</v>
+        <v>0.2650806802742173</v>
       </c>
     </row>
     <row r="8">
@@ -1017,67 +1017,67 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>50679</v>
+        <v>61449</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>44946</v>
+        <v>55127</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>56761</v>
+        <v>67372</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.7378769020846165</v>
+        <v>0.765914179383742</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.6544013836712529</v>
+        <v>0.6871179287342181</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.8264342618505098</v>
+        <v>0.8397340138660596</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>57103</v>
+        <v>64187</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>50616</v>
+        <v>57981</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>61873</v>
+        <v>69277</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.8105966569948891</v>
+        <v>0.8279039082609307</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.7185112287418057</v>
+        <v>0.747858759495762</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.8783068474796145</v>
+        <v>0.8935464354187939</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>156</v>
+        <v>182</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>107782</v>
+        <v>125637</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>99355</v>
+        <v>115941</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>115065</v>
+        <v>132834</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.7746976350773396</v>
+        <v>0.7963786294674613</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.7141275589081139</v>
+        <v>0.7349193197257827</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.8270457706782314</v>
+        <v>0.8420003821069724</v>
       </c>
     </row>
     <row r="9">
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>68682</v>
+        <v>80230</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>68682</v>
+        <v>80230</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>68682</v>
+        <v>80230</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -1109,16 +1109,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>70446</v>
+        <v>77530</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>70446</v>
+        <v>77530</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>70446</v>
+        <v>77530</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -1130,16 +1130,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>201</v>
+        <v>228</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>139128</v>
+        <v>157760</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>139128</v>
+        <v>157760</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>139128</v>
+        <v>157760</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -1169,61 +1169,61 @@
         <v>19063</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>13562</v>
+        <v>12937</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>25372</v>
+        <v>25187</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.3118627533986425</v>
+        <v>0.2817590936869661</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.2218697165448557</v>
+        <v>0.1912135242966658</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.4150793136719574</v>
+        <v>0.3722862068787268</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>12597</v>
+        <v>13364</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>7812</v>
+        <v>8753</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>18765</v>
+        <v>18964</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.2036011594003728</v>
+        <v>0.1862314719444784</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.1262611901400157</v>
+        <v>0.1219732479498272</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.3033086245161741</v>
+        <v>0.2642659753689749</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>31659</v>
+        <v>32427</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>23682</v>
+        <v>24690</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>39888</v>
+        <v>41893</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.2574049180740419</v>
+        <v>0.2325885565132677</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.1925462309236269</v>
+        <v>0.1770929733952184</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.3243125223681464</v>
+        <v>0.300484478368391</v>
       </c>
     </row>
     <row r="11">
@@ -1234,67 +1234,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>42063</v>
+        <v>48593</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>35754</v>
+        <v>42469</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>47564</v>
+        <v>54719</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.6881372466013574</v>
+        <v>0.7182409063130339</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.5849206863280425</v>
+        <v>0.6277137931212734</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.7781302834551442</v>
+        <v>0.8087864757033343</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>49272</v>
+        <v>58398</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>43104</v>
+        <v>52798</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>54057</v>
+        <v>63009</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.7963988405996272</v>
+        <v>0.8137685280555216</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.6966913754838262</v>
+        <v>0.7357340246310252</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.8737388098599843</v>
+        <v>0.8780267520501727</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>91335</v>
+        <v>106992</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>83106</v>
+        <v>97526</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>99312</v>
+        <v>114729</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.7425950819259581</v>
+        <v>0.7674114434867323</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.6756874776318534</v>
+        <v>0.6995155216316099</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.807453769076373</v>
+        <v>0.8229070266047822</v>
       </c>
     </row>
     <row r="12">
@@ -1305,16 +1305,16 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>61126</v>
+        <v>67656</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>61126</v>
+        <v>67656</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>61126</v>
+        <v>67656</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>1</v>
@@ -1326,16 +1326,16 @@
         <v>1</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>61869</v>
+        <v>71762</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>61869</v>
+        <v>71762</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>61869</v>
+        <v>71762</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>1</v>
@@ -1347,16 +1347,16 @@
         <v>1</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>178</v>
+        <v>203</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>122994</v>
+        <v>139419</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>122994</v>
+        <v>139419</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>122994</v>
+        <v>139419</v>
       </c>
       <c r="U12" s="6" t="n">
         <v>1</v>
@@ -1380,67 +1380,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>44902</v>
+        <v>50598</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>35846</v>
+        <v>41245</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>54793</v>
+        <v>61823</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.288832753011954</v>
+        <v>0.269512183944968</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.2305848689190227</v>
+        <v>0.2196953919803714</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.3524582028493574</v>
+        <v>0.32930501509667</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>30695</v>
+        <v>36063</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>22486</v>
+        <v>28250</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>39841</v>
+        <v>45409</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.2330034155063735</v>
+        <v>0.2197191641661296</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.1706893972596205</v>
+        <v>0.1721186285759744</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.3024273895379906</v>
+        <v>0.2766611661176092</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>75597</v>
+        <v>86661</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>64056</v>
+        <v>74156</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>89370</v>
+        <v>100172</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.2632239230934917</v>
+        <v>0.246285799814924</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.2230408300817361</v>
+        <v>0.2107478580226003</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.3111823461615225</v>
+        <v>0.2846845071639049</v>
       </c>
     </row>
     <row r="14">
@@ -1451,67 +1451,67 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>159</v>
+        <v>197</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>110557</v>
+        <v>137140</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>100666</v>
+        <v>125915</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>119613</v>
+        <v>146493</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.711167246988046</v>
+        <v>0.730487816055032</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.6475417971506432</v>
+        <v>0.6706949849033303</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.7694151310809774</v>
+        <v>0.7803046080196285</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>146</v>
+        <v>186</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>101041</v>
+        <v>128070</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>91895</v>
+        <v>118724</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>109250</v>
+        <v>135883</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.7669965844936265</v>
+        <v>0.7802808358338703</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.6975726104620094</v>
+        <v>0.7233388338823908</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.8293106027403795</v>
+        <v>0.8278813714240256</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>305</v>
+        <v>383</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>211598</v>
+        <v>265210</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>197825</v>
+        <v>251699</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>223139</v>
+        <v>277715</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.7367760769065083</v>
+        <v>0.753714200185076</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.6888176538384778</v>
+        <v>0.7153154928360951</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.7769591699182639</v>
+        <v>0.7892521419773998</v>
       </c>
     </row>
     <row r="15">
@@ -1522,16 +1522,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>223</v>
+        <v>269</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>155459</v>
+        <v>187738</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>155459</v>
+        <v>187738</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>155459</v>
+        <v>187738</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -1543,16 +1543,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>190</v>
+        <v>237</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>131736</v>
+        <v>164133</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>131736</v>
+        <v>164133</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>131736</v>
+        <v>164133</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -1564,16 +1564,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>413</v>
+        <v>506</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>287195</v>
+        <v>351871</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>287195</v>
+        <v>351871</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>287195</v>
+        <v>351871</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -1597,67 +1597,67 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>35699</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>27577</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>44415</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.2892265171204015</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.2234251131941634</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.3598358839675305</v>
+      </c>
+      <c r="J16" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="D16" s="5" t="n">
-        <v>29530</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>22624</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>37490</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>0.2993130855931196</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>0.2293119089207572</v>
-      </c>
-      <c r="I16" s="6" t="n">
-        <v>0.3799963999626317</v>
-      </c>
-      <c r="J16" s="5" t="n">
-        <v>35</v>
-      </c>
       <c r="K16" s="5" t="n">
-        <v>24069</v>
+        <v>29363</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>18042</v>
+        <v>21748</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>32066</v>
+        <v>37522</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.2218046949306867</v>
+        <v>0.2258881950024376</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.1662613150070337</v>
+        <v>0.1673088479970622</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.2954958530774942</v>
+        <v>0.2886569968521557</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>53599</v>
+        <v>65062</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>43418</v>
+        <v>54105</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>64157</v>
+        <v>77218</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.2587150676838008</v>
+        <v>0.2567377540033388</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.209574975683876</v>
+        <v>0.2134992299690018</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.3096782822864353</v>
+        <v>0.3047064691356323</v>
       </c>
     </row>
     <row r="17">
@@ -1668,67 +1668,67 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>69129</v>
+        <v>87731</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>61169</v>
+        <v>79015</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>76035</v>
+        <v>95853</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.7006869144068804</v>
+        <v>0.7107734828795985</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.6200036000373684</v>
+        <v>0.6401641160324696</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.7706880910792427</v>
+        <v>0.7765748868058365</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>84446</v>
+        <v>100625</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>76449</v>
+        <v>92466</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>90473</v>
+        <v>108240</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.7781953050693133</v>
+        <v>0.7741118049975624</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.7045041469225057</v>
+        <v>0.7113430031478443</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.8337386849929662</v>
+        <v>0.8326911520029378</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>218</v>
+        <v>268</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>153575</v>
+        <v>188356</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>143017</v>
+        <v>176200</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>163756</v>
+        <v>199313</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.7412849323161992</v>
+        <v>0.7432622459966612</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.6903217177135647</v>
+        <v>0.6952935308643676</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.7904250243161239</v>
+        <v>0.7865007700309982</v>
       </c>
     </row>
     <row r="18">
@@ -1739,16 +1739,16 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>140</v>
+        <v>174</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>98659</v>
+        <v>123430</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>98659</v>
+        <v>123430</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>98659</v>
+        <v>123430</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>1</v>
@@ -1760,16 +1760,16 @@
         <v>1</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>108515</v>
+        <v>129988</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>108515</v>
+        <v>129988</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>108515</v>
+        <v>129988</v>
       </c>
       <c r="N18" s="6" t="n">
         <v>1</v>
@@ -1781,16 +1781,16 @@
         <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>295</v>
+        <v>359</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>207174</v>
+        <v>253418</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>207174</v>
+        <v>253418</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>207174</v>
+        <v>253418</v>
       </c>
       <c r="U18" s="6" t="n">
         <v>1</v>
@@ -1814,67 +1814,67 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>16823</v>
+        <v>17496</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>11801</v>
+        <v>11689</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>22779</v>
+        <v>23813</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.3112176103058159</v>
+        <v>0.2787339409584163</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.2183083569556674</v>
+        <v>0.1862180805601615</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.4214047530778381</v>
+        <v>0.3793678708188071</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>11634</v>
+        <v>13457</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>7533</v>
+        <v>8616</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>16569</v>
+        <v>19011</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.2839244973561185</v>
+        <v>0.29912851672487</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.1838532673474886</v>
+        <v>0.1915089365076081</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.4043774760820137</v>
+        <v>0.4225770375594928</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="R19" s="5" t="n">
-        <v>28457</v>
+        <v>30954</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>21790</v>
+        <v>23829</v>
       </c>
       <c r="T19" s="5" t="n">
-        <v>36950</v>
+        <v>39293</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0.299449655213627</v>
+        <v>0.287248564003138</v>
       </c>
       <c r="V19" s="6" t="n">
-        <v>0.2292927307352631</v>
+        <v>0.2211282582368756</v>
       </c>
       <c r="W19" s="6" t="n">
-        <v>0.3888247968658628</v>
+        <v>0.3646353622991118</v>
       </c>
     </row>
     <row r="20">
@@ -1885,67 +1885,67 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>37233</v>
+        <v>45275</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>31277</v>
+        <v>38958</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>42255</v>
+        <v>51082</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.688782389694184</v>
+        <v>0.7212660590415837</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.5785952469221618</v>
+        <v>0.6206321291811927</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.7816916430443314</v>
+        <v>0.8137819194398381</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>29340</v>
+        <v>31532</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>24405</v>
+        <v>25978</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>33441</v>
+        <v>36373</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.7160755026438815</v>
+        <v>0.70087148327513</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.5956225239179862</v>
+        <v>0.5774229624405074</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.8161467326525114</v>
+        <v>0.808491063492392</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="R20" s="5" t="n">
-        <v>66574</v>
+        <v>76806</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>58081</v>
+        <v>68467</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>73241</v>
+        <v>83931</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.700550344786373</v>
+        <v>0.712751435996862</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.6111752031341372</v>
+        <v>0.6353646377008882</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.7707072692647369</v>
+        <v>0.7788717417631245</v>
       </c>
     </row>
     <row r="21">
@@ -1956,16 +1956,16 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>54056</v>
+        <v>62771</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>54056</v>
+        <v>62771</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>54056</v>
+        <v>62771</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>1</v>
@@ -1977,16 +1977,16 @@
         <v>1</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>40974</v>
+        <v>44989</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>40974</v>
+        <v>44989</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>40974</v>
+        <v>44989</v>
       </c>
       <c r="N21" s="6" t="n">
         <v>1</v>
@@ -1998,16 +1998,16 @@
         <v>1</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>95031</v>
+        <v>107760</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>95031</v>
+        <v>107760</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>95031</v>
+        <v>107760</v>
       </c>
       <c r="U21" s="6" t="n">
         <v>1</v>
@@ -2031,67 +2031,67 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>140850</v>
+        <v>154165</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>125445</v>
+        <v>138399</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>158987</v>
+        <v>171449</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.2842758216275966</v>
+        <v>0.2607955691213584</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.2531854981751872</v>
+        <v>0.2341246810968234</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.3208814973580582</v>
+        <v>0.2900331570426288</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>107241</v>
+        <v>121752</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>92253</v>
+        <v>105852</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>122301</v>
+        <v>137256</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.2233071532372957</v>
+        <v>0.2156045438440373</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.1920973944126468</v>
+        <v>0.1874472850717156</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.2546669378437136</v>
+        <v>0.2430602353152329</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>355</v>
+        <v>391</v>
       </c>
       <c r="R22" s="5" t="n">
-        <v>248091</v>
+        <v>275917</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>228037</v>
+        <v>252467</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>271085</v>
+        <v>298751</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.2542672437833857</v>
+        <v>0.2387168079875909</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.2337139722453175</v>
+        <v>0.2184277538125873</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.2778339588419336</v>
+        <v>0.2584719750620495</v>
       </c>
     </row>
     <row r="23">
@@ -2102,67 +2102,67 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>512</v>
+        <v>631</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>354618</v>
+        <v>436970</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>336481</v>
+        <v>419686</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>370023</v>
+        <v>452736</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.7157241783724033</v>
+        <v>0.7392044308786416</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.6791185026419418</v>
+        <v>0.7099668429573712</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.7468145018248129</v>
+        <v>0.7658753189031766</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>534</v>
+        <v>637</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>372999</v>
+        <v>442949</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>357939</v>
+        <v>427445</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>387987</v>
+        <v>458849</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.7766928467627042</v>
+        <v>0.7843954561559627</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.7453330621562863</v>
+        <v>0.756939764684767</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.8079026055873531</v>
+        <v>0.8125527149282844</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>1046</v>
+        <v>1268</v>
       </c>
       <c r="R23" s="5" t="n">
-        <v>727617</v>
+        <v>879919</v>
       </c>
       <c r="S23" s="5" t="n">
-        <v>704623</v>
+        <v>857085</v>
       </c>
       <c r="T23" s="5" t="n">
-        <v>747671</v>
+        <v>903369</v>
       </c>
       <c r="U23" s="6" t="n">
-        <v>0.7457327562166144</v>
+        <v>0.7612831920124091</v>
       </c>
       <c r="V23" s="6" t="n">
-        <v>0.7221660411580664</v>
+        <v>0.7415280249379508</v>
       </c>
       <c r="W23" s="6" t="n">
-        <v>0.7662860277546825</v>
+        <v>0.7815722461874127</v>
       </c>
     </row>
     <row r="24">
@@ -2173,16 +2173,16 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>712</v>
+        <v>848</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>495468</v>
+        <v>591135</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>495468</v>
+        <v>591135</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>495468</v>
+        <v>591135</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>1</v>
@@ -2194,16 +2194,16 @@
         <v>1</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>689</v>
+        <v>811</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>480240</v>
+        <v>564701</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>480240</v>
+        <v>564701</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>480240</v>
+        <v>564701</v>
       </c>
       <c r="N24" s="6" t="n">
         <v>1</v>
@@ -2215,16 +2215,16 @@
         <v>1</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>1401</v>
+        <v>1659</v>
       </c>
       <c r="R24" s="5" t="n">
-        <v>975708</v>
+        <v>1155836</v>
       </c>
       <c r="S24" s="5" t="n">
-        <v>975708</v>
+        <v>1155836</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>975708</v>
+        <v>1155836</v>
       </c>
       <c r="U24" s="6" t="n">
         <v>1</v>
@@ -2298,7 +2298,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido en 2016 (tasa de respuesta: 69,19%)</t>
+          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido en 2016 (tasa de respuesta: 82,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2482,67 +2482,67 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>12537</v>
+        <v>13113</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>8147</v>
+        <v>8278</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>17958</v>
+        <v>18863</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.1935426857007771</v>
+        <v>0.1648221900077274</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.1257706348962283</v>
+        <v>0.1040572549031738</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.2772350859211987</v>
+        <v>0.237103632574856</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>7954</v>
+        <v>8423</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>4552</v>
+        <v>5128</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>13650</v>
+        <v>14339</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.1495397773366751</v>
+        <v>0.1332856190281185</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.08557274615100688</v>
+        <v>0.08115059974647701</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.2566276657187054</v>
+        <v>0.2269096318096814</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>20491</v>
+        <v>21535</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>14875</v>
+        <v>15024</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>27939</v>
+        <v>28888</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.1737025224448562</v>
+        <v>0.1508615495216</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.1260983684615845</v>
+        <v>0.1052489288345762</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.2368418201736078</v>
+        <v>0.2023751709133279</v>
       </c>
     </row>
     <row r="5">
@@ -2553,67 +2553,67 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>52240</v>
+        <v>66443</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>46819</v>
+        <v>60693</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>56630</v>
+        <v>71278</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.8064573142992228</v>
+        <v>0.8351778099922726</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.7227649140788014</v>
+        <v>0.762896367425144</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.8742293651037721</v>
+        <v>0.8959427450968264</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>45235</v>
+        <v>54769</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>39539</v>
+        <v>48853</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>48637</v>
+        <v>58064</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.8504602226633249</v>
+        <v>0.8667143809718815</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.7433723342812946</v>
+        <v>0.7730903681903187</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.9144272538489931</v>
+        <v>0.918849400253523</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>142</v>
+        <v>178</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>97475</v>
+        <v>121212</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>90027</v>
+        <v>113859</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>103091</v>
+        <v>127723</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.8262974775551438</v>
+        <v>0.8491384504784</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.7631581798263923</v>
+        <v>0.7976248290866722</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.8739016315384156</v>
+        <v>0.8947510711654237</v>
       </c>
     </row>
     <row r="6">
@@ -2624,16 +2624,16 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>64777</v>
+        <v>79556</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>64777</v>
+        <v>79556</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>64777</v>
+        <v>79556</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
@@ -2645,16 +2645,16 @@
         <v>1</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>53189</v>
+        <v>63192</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>53189</v>
+        <v>63192</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>53189</v>
+        <v>63192</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>1</v>
@@ -2666,16 +2666,16 @@
         <v>1</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>173</v>
+        <v>211</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>117966</v>
+        <v>142747</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>117966</v>
+        <v>142747</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>117966</v>
+        <v>142747</v>
       </c>
       <c r="U6" s="6" t="n">
         <v>1</v>
@@ -2699,67 +2699,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>12298</v>
+        <v>13775</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>7913</v>
+        <v>8472</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>18156</v>
+        <v>20253</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.1489505062419707</v>
+        <v>0.1456988502669421</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.09584062740568858</v>
+        <v>0.08961196604266979</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.2198931290975886</v>
+        <v>0.2142204263084874</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>4778</v>
+        <v>6817</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>2321</v>
+        <v>3639</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>8976</v>
+        <v>11531</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.06839138560369563</v>
+        <v>0.08238392126666584</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.0332160264209529</v>
+        <v>0.04397814717924489</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.1284815901505456</v>
+        <v>0.1393499673112803</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>17076</v>
+        <v>20592</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>11834</v>
+        <v>14222</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>23599</v>
+        <v>28231</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.1120280594920845</v>
+        <v>0.1161475472666146</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.07763271652953001</v>
+        <v>0.0802192937241936</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.1548178453029425</v>
+        <v>0.159234678774876</v>
       </c>
     </row>
     <row r="8">
@@ -2770,67 +2770,67 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>70269</v>
+        <v>80769</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>64411</v>
+        <v>74291</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>74654</v>
+        <v>86072</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.8510494937580293</v>
+        <v>0.8543011497330579</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.7801068709024114</v>
+        <v>0.7857795736915127</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.9041593725943113</v>
+        <v>0.9103880339573303</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>65085</v>
+        <v>75931</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>60887</v>
+        <v>71217</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>67542</v>
+        <v>79109</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.9316086143963044</v>
+        <v>0.9176160787333342</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.8715184098494548</v>
+        <v>0.8606500326887196</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.9667839735790472</v>
+        <v>0.9560218528207551</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>197</v>
+        <v>228</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>135354</v>
+        <v>156700</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>128831</v>
+        <v>149061</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>140596</v>
+        <v>163070</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.8879719405079155</v>
+        <v>0.8838524527333853</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.8451821546970575</v>
+        <v>0.8407653212251242</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.9223672834704699</v>
+        <v>0.9197807062758065</v>
       </c>
     </row>
     <row r="9">
@@ -2841,16 +2841,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>82567</v>
+        <v>94544</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>82567</v>
+        <v>94544</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>82567</v>
+        <v>94544</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -2862,16 +2862,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>69863</v>
+        <v>82748</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>69863</v>
+        <v>82748</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>69863</v>
+        <v>82748</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -2883,16 +2883,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>223</v>
+        <v>259</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>152430</v>
+        <v>177292</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>152430</v>
+        <v>177292</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>152430</v>
+        <v>177292</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -2916,67 +2916,67 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>15741</v>
+        <v>17017</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>10807</v>
+        <v>11413</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>22234</v>
+        <v>22545</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.2753030032398064</v>
+        <v>0.2637757123016692</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.1889986431303466</v>
+        <v>0.1769006079123047</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.388860465686619</v>
+        <v>0.3494582966109764</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>4691</v>
+        <v>5864</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>1950</v>
+        <v>3057</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>9047</v>
+        <v>10221</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.1025289851505094</v>
+        <v>0.1110926102059442</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.04263238316819332</v>
+        <v>0.05791888662962349</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.1977537963984085</v>
+        <v>0.1936400484717098</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>20432</v>
+        <v>22881</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>14250</v>
+        <v>16573</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>27214</v>
+        <v>30336</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.1985077806334933</v>
+        <v>0.1950691760338673</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.1384429311288386</v>
+        <v>0.141285430476938</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.2644011340342674</v>
+        <v>0.258620262371637</v>
       </c>
     </row>
     <row r="11">
@@ -2987,67 +2987,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>41437</v>
+        <v>47498</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>34944</v>
+        <v>41970</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>46371</v>
+        <v>53102</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.7246969967601936</v>
+        <v>0.7362242876983308</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.6111395343133806</v>
+        <v>0.6505417033890242</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.8110013568696532</v>
+        <v>0.8230993920876953</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>41059</v>
+        <v>46920</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>36703</v>
+        <v>42563</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>43800</v>
+        <v>49727</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.8974710148494905</v>
+        <v>0.8889073897940558</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.8022462036015916</v>
+        <v>0.8063599515282905</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.9573676168318067</v>
+        <v>0.9420811133703765</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>82496</v>
+        <v>94418</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>75714</v>
+        <v>86963</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>88678</v>
+        <v>100726</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.8014922193665067</v>
+        <v>0.8049308239661327</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.7355988659657327</v>
+        <v>0.7413797376283637</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.8615570688711615</v>
+        <v>0.8587145695230621</v>
       </c>
     </row>
     <row r="12">
@@ -3058,16 +3058,16 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>57178</v>
+        <v>64515</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>57178</v>
+        <v>64515</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>57178</v>
+        <v>64515</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>1</v>
@@ -3079,16 +3079,16 @@
         <v>1</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>45750</v>
+        <v>52784</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>45750</v>
+        <v>52784</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>45750</v>
+        <v>52784</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>1</v>
@@ -3100,16 +3100,16 @@
         <v>1</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>102928</v>
+        <v>117299</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>102928</v>
+        <v>117299</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>102928</v>
+        <v>117299</v>
       </c>
       <c r="U12" s="6" t="n">
         <v>1</v>
@@ -3133,67 +3133,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>30635</v>
+        <v>37308</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>23529</v>
+        <v>28576</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>39904</v>
+        <v>47697</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.2117084400358848</v>
+        <v>0.2053890418566688</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.1625974105983069</v>
+        <v>0.1573153418491808</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.2757557741585625</v>
+        <v>0.262583199647571</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>23572</v>
+        <v>24771</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>16918</v>
+        <v>18333</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>32074</v>
+        <v>33208</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.1564263044890468</v>
+        <v>0.1376356353991957</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.1122677960725125</v>
+        <v>0.1018681422038791</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.2128466313853609</v>
+        <v>0.184518591002113</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>54207</v>
+        <v>62079</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>43609</v>
+        <v>51658</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>66210</v>
+        <v>75671</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.1835075450692938</v>
+        <v>0.1716692100711909</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.1476306473114343</v>
+        <v>0.1428515068493872</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.2241408439924501</v>
+        <v>0.209257513726245</v>
       </c>
     </row>
     <row r="14">
@@ -3204,67 +3204,67 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>161</v>
+        <v>205</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>114071</v>
+        <v>144339</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>104802</v>
+        <v>133950</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>121177</v>
+        <v>153071</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.7882915599641152</v>
+        <v>0.7946109581433312</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.7242442258414375</v>
+        <v>0.7374168003524288</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.8374025894016931</v>
+        <v>0.8426846581508192</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>192</v>
+        <v>234</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>127117</v>
+        <v>155201</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>118615</v>
+        <v>146764</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>133771</v>
+        <v>161639</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.8435736955109532</v>
+        <v>0.8623643646008042</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.7871533686146398</v>
+        <v>0.8154814089978869</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.8877322039274876</v>
+        <v>0.8981318577961209</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>353</v>
+        <v>439</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>241188</v>
+        <v>299540</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>229185</v>
+        <v>285948</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>251786</v>
+        <v>309961</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.8164924549307062</v>
+        <v>0.8283307899288092</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.77585915600755</v>
+        <v>0.790742486273755</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.8523693526885657</v>
+        <v>0.8571484931506128</v>
       </c>
     </row>
     <row r="15">
@@ -3275,16 +3275,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>205</v>
+        <v>257</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>144706</v>
+        <v>181647</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>144706</v>
+        <v>181647</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>144706</v>
+        <v>181647</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -3296,16 +3296,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>228</v>
+        <v>272</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>150689</v>
+        <v>179972</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>150689</v>
+        <v>179972</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>150689</v>
+        <v>179972</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -3317,16 +3317,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>433</v>
+        <v>529</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>295395</v>
+        <v>361619</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>295395</v>
+        <v>361619</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>295395</v>
+        <v>361619</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -3350,67 +3350,67 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>22867</v>
+        <v>24697</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>16006</v>
+        <v>18071</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>30673</v>
+        <v>32886</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.2262189308312182</v>
+        <v>0.1996882834735372</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.1583425777218756</v>
+        <v>0.1461161596829173</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.3034394050437326</v>
+        <v>0.2659039579458326</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>14579</v>
+        <v>15949</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>9647</v>
+        <v>10713</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>20906</v>
+        <v>22311</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.1496985113309979</v>
+        <v>0.1327149118007199</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.09905641812577595</v>
+        <v>0.08914352417634014</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.214668480818741</v>
+        <v>0.1856587197786868</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>37446</v>
+        <v>40646</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>28632</v>
+        <v>31589</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>46873</v>
+        <v>51266</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.1886709975480347</v>
+        <v>0.1666828884986559</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.1442620783594991</v>
+        <v>0.1295402620595634</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.2361669867487948</v>
+        <v>0.2102340945521037</v>
       </c>
     </row>
     <row r="17">
@@ -3421,67 +3421,67 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>78217</v>
+        <v>98981</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>70411</v>
+        <v>90792</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>85078</v>
+        <v>105607</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.7737810691687818</v>
+        <v>0.8003117165264628</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.6965605949562677</v>
+        <v>0.7340960420541675</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.8416574222781243</v>
+        <v>0.8538838403170826</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>122</v>
+        <v>154</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>82810</v>
+        <v>104225</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>76483</v>
+        <v>97863</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>87742</v>
+        <v>109461</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.8503014886690021</v>
+        <v>0.8672850881992801</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.785331519181259</v>
+        <v>0.8143412802213132</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.9009435818742241</v>
+        <v>0.9108564758236599</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>231</v>
+        <v>291</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>161026</v>
+        <v>203206</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>151599</v>
+        <v>192586</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>169840</v>
+        <v>212263</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.8113290024519654</v>
+        <v>0.8333171115013441</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.7638330132512052</v>
+        <v>0.7897659054478963</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.8557379216405009</v>
+        <v>0.8704597379404364</v>
       </c>
     </row>
     <row r="18">
@@ -3492,16 +3492,16 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>101084</v>
+        <v>123678</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>101084</v>
+        <v>123678</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>101084</v>
+        <v>123678</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>1</v>
@@ -3513,16 +3513,16 @@
         <v>1</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>145</v>
+        <v>179</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>97389</v>
+        <v>120174</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>97389</v>
+        <v>120174</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>97389</v>
+        <v>120174</v>
       </c>
       <c r="N18" s="6" t="n">
         <v>1</v>
@@ -3534,16 +3534,16 @@
         <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>285</v>
+        <v>350</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>198472</v>
+        <v>243852</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>198472</v>
+        <v>243852</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>198472</v>
+        <v>243852</v>
       </c>
       <c r="U18" s="6" t="n">
         <v>1</v>
@@ -3567,25 +3567,25 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>11674</v>
+        <v>13633</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>7052</v>
+        <v>9084</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>17589</v>
+        <v>19072</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.232069245166383</v>
+        <v>0.2338471589112371</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.1401914384996414</v>
+        <v>0.1558118492171937</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.3496419283609253</v>
+        <v>0.3271425931932774</v>
       </c>
       <c r="J19" s="5" t="n">
         <v>10</v>
@@ -3594,40 +3594,40 @@
         <v>7310</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>3795</v>
+        <v>3957</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>12706</v>
+        <v>12588</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.1671191472339087</v>
+        <v>0.150358239705164</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.08675342548251153</v>
+        <v>0.08138496705450668</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.2904612117073092</v>
+        <v>0.2589185918626215</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="R19" s="5" t="n">
-        <v>18985</v>
+        <v>20943</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>13313</v>
+        <v>14115</v>
       </c>
       <c r="T19" s="5" t="n">
-        <v>26331</v>
+        <v>28075</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0.2018604432533457</v>
+        <v>0.1958815757051213</v>
       </c>
       <c r="V19" s="6" t="n">
-        <v>0.141552029240342</v>
+        <v>0.1320125720186946</v>
       </c>
       <c r="W19" s="6" t="n">
-        <v>0.2799669041975941</v>
+        <v>0.2625858487696707</v>
       </c>
     </row>
     <row r="20">
@@ -3638,67 +3638,67 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>38632</v>
+        <v>44665</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>32717</v>
+        <v>39226</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>43254</v>
+        <v>49214</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.7679307548336171</v>
+        <v>0.7661528410887629</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.6503580716390746</v>
+        <v>0.6728574068067226</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.8598085615003586</v>
+        <v>0.8441881507828064</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>36433</v>
+        <v>41309</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>31037</v>
+        <v>36031</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>39948</v>
+        <v>44662</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.8328808527660913</v>
+        <v>0.8496417602948361</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.7095387882926908</v>
+        <v>0.7410814081373783</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.9132465745174885</v>
+        <v>0.9186150329454932</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="R20" s="5" t="n">
-        <v>75065</v>
+        <v>85975</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>67719</v>
+        <v>78843</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>80737</v>
+        <v>92803</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.7981395567466543</v>
+        <v>0.8041184242948787</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.7200330958024058</v>
+        <v>0.7374141512303293</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.858447970759658</v>
+        <v>0.8679874279813053</v>
       </c>
     </row>
     <row r="21">
@@ -3709,37 +3709,37 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>58298</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>58298</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>58298</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="5" t="n">
         <v>71</v>
       </c>
-      <c r="D21" s="5" t="n">
-        <v>50306</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>50306</v>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>50306</v>
-      </c>
-      <c r="G21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="5" t="n">
-        <v>63</v>
-      </c>
       <c r="K21" s="5" t="n">
-        <v>43743</v>
+        <v>48619</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>43743</v>
+        <v>48619</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>43743</v>
+        <v>48619</v>
       </c>
       <c r="N21" s="6" t="n">
         <v>1</v>
@@ -3751,16 +3751,16 @@
         <v>1</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>94050</v>
+        <v>106918</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>94050</v>
+        <v>106918</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>94050</v>
+        <v>106918</v>
       </c>
       <c r="U21" s="6" t="n">
         <v>1</v>
@@ -3784,67 +3784,67 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>105754</v>
+        <v>119543</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>90821</v>
+        <v>104235</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>121013</v>
+        <v>136580</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.2112465556139622</v>
+        <v>0.1984983637635648</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.1814177924395368</v>
+        <v>0.1730794203173929</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.2417273581589527</v>
+        <v>0.2267875022601232</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>62883</v>
+        <v>69133</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>51515</v>
+        <v>58135</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>74882</v>
+        <v>82566</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.1365186101494964</v>
+        <v>0.1262734130663447</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.1118368538296248</v>
+        <v>0.1061853960882611</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.1625670908932944</v>
+        <v>0.1508089432480762</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>249</v>
+        <v>278</v>
       </c>
       <c r="R22" s="5" t="n">
-        <v>168637</v>
+        <v>188677</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>150802</v>
+        <v>167065</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>188822</v>
+        <v>207598</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.1754372607237008</v>
+        <v>0.1641055216696947</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.1568826406308443</v>
+        <v>0.1453084892233821</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.1964351298779729</v>
+        <v>0.1805624777594108</v>
       </c>
     </row>
     <row r="23">
@@ -3855,67 +3855,67 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>561</v>
+        <v>686</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>394864</v>
+        <v>482695</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>379605</v>
+        <v>465658</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>409797</v>
+        <v>498003</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.7887534443860378</v>
+        <v>0.8015016362364352</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.7582726418410488</v>
+        <v>0.7732124977398762</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.8185822075604633</v>
+        <v>0.8269205796826069</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>591</v>
+        <v>713</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>397739</v>
+        <v>478356</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>385740</v>
+        <v>464923</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>409107</v>
+        <v>489354</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.8634813898505036</v>
+        <v>0.8737265869336552</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.8374329091067066</v>
+        <v>0.8491910567519241</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.8881631461703752</v>
+        <v>0.8938146039117389</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>1152</v>
+        <v>1399</v>
       </c>
       <c r="R23" s="5" t="n">
-        <v>792604</v>
+        <v>961050</v>
       </c>
       <c r="S23" s="5" t="n">
-        <v>772419</v>
+        <v>942129</v>
       </c>
       <c r="T23" s="5" t="n">
-        <v>810439</v>
+        <v>982662</v>
       </c>
       <c r="U23" s="6" t="n">
-        <v>0.8245627392762992</v>
+        <v>0.8358944783303053</v>
       </c>
       <c r="V23" s="6" t="n">
-        <v>0.803564870122027</v>
+        <v>0.8194375222405894</v>
       </c>
       <c r="W23" s="6" t="n">
-        <v>0.8431173593691557</v>
+        <v>0.854691510776618</v>
       </c>
     </row>
     <row r="24">
@@ -3926,16 +3926,16 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>713</v>
+        <v>857</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>500618</v>
+        <v>602238</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>500618</v>
+        <v>602238</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>500618</v>
+        <v>602238</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>1</v>
@@ -3947,16 +3947,16 @@
         <v>1</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>688</v>
+        <v>820</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>460622</v>
+        <v>547489</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>460622</v>
+        <v>547489</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>460622</v>
+        <v>547489</v>
       </c>
       <c r="N24" s="6" t="n">
         <v>1</v>
@@ -3968,16 +3968,16 @@
         <v>1</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>1401</v>
+        <v>1677</v>
       </c>
       <c r="R24" s="5" t="n">
-        <v>961241</v>
+        <v>1149727</v>
       </c>
       <c r="S24" s="5" t="n">
-        <v>961241</v>
+        <v>1149727</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>961241</v>
+        <v>1149727</v>
       </c>
       <c r="U24" s="6" t="n">
         <v>1</v>
@@ -4051,7 +4051,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido en 2023 (tasa de respuesta: 78,24%)</t>
+          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido en 2023 (tasa de respuesta: 82,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4241,19 +4241,19 @@
         <v>5158</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>2238</v>
+        <v>2315</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>9446</v>
+        <v>9747</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.09666615979837974</v>
+        <v>0.09222367574974095</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.04193362774548676</v>
+        <v>0.04138379801810717</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.1770214391538174</v>
+        <v>0.1742732040567143</v>
       </c>
       <c r="J4" s="5" t="n">
         <v>6</v>
@@ -4262,19 +4262,19 @@
         <v>4164</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>1653</v>
+        <v>1764</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>9397</v>
+        <v>8959</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.1049150594486263</v>
+        <v>0.102680748143465</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.04164228146453473</v>
+        <v>0.04350124745005089</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.2367517391009363</v>
+        <v>0.2209070341042098</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>14</v>
@@ -4283,19 +4283,19 @@
         <v>9322</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>5260</v>
+        <v>5170</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>15512</v>
+        <v>15242</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.1001847543884441</v>
+        <v>0.09661902240265521</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.05652926442093679</v>
+        <v>0.05358413285378695</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.1667077857833121</v>
+        <v>0.1579703110603378</v>
       </c>
     </row>
     <row r="5">
@@ -4306,67 +4306,67 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>48202</v>
+        <v>50772</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>43914</v>
+        <v>46183</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>51122</v>
+        <v>53615</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.9033338402016203</v>
+        <v>0.907776324250259</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.8229785608461841</v>
+        <v>0.8257267959432854</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.9580663722545136</v>
+        <v>0.9586162019818928</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>35527</v>
+        <v>36391</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>30294</v>
+        <v>31596</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>38038</v>
+        <v>38791</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.8950849405513736</v>
+        <v>0.8973192518565349</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.7632482608990639</v>
+        <v>0.7790929658957894</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.9583577185354655</v>
+        <v>0.9564987525499489</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>83729</v>
+        <v>87163</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>77539</v>
+        <v>81243</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>87791</v>
+        <v>91315</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.8998152456115558</v>
+        <v>0.9033809775973447</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.8332922142166876</v>
+        <v>0.8420296889396622</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.943470735579063</v>
+        <v>0.9464158671462132</v>
       </c>
     </row>
     <row r="6">
@@ -4377,16 +4377,16 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>53360</v>
+        <v>55930</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>53360</v>
+        <v>55930</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>53360</v>
+        <v>55930</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
@@ -4398,16 +4398,16 @@
         <v>1</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>39691</v>
+        <v>40555</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>39691</v>
+        <v>40555</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>39691</v>
+        <v>40555</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>1</v>
@@ -4419,16 +4419,16 @@
         <v>1</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>93051</v>
+        <v>96485</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>93051</v>
+        <v>96485</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>93051</v>
+        <v>96485</v>
       </c>
       <c r="U6" s="6" t="n">
         <v>1</v>
@@ -4458,19 +4458,19 @@
         <v>7038</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>3591</v>
+        <v>3266</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>11988</v>
+        <v>11908</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.1687255768262762</v>
+        <v>0.1661710145117522</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.0860973940462334</v>
+        <v>0.07712116897213839</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.2873889728646655</v>
+        <v>0.2811496967577831</v>
       </c>
       <c r="J7" s="5" t="n">
         <v>7</v>
@@ -4479,19 +4479,19 @@
         <v>3463</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>1426</v>
+        <v>1398</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>7204</v>
+        <v>7148</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.08657310316396408</v>
+        <v>0.08093628841346513</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.03564913305339732</v>
+        <v>0.03268481374199971</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.1800804247229498</v>
+        <v>0.1670669936050407</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>17</v>
@@ -4500,19 +4500,19 @@
         <v>10501</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>6568</v>
+        <v>6294</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>16687</v>
+        <v>16125</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.1285093319931687</v>
+        <v>0.1233364819584688</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.08037999904561502</v>
+        <v>0.07392980561045333</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.2042176840136879</v>
+        <v>0.1893864955423283</v>
       </c>
     </row>
     <row r="8">
@@ -4523,67 +4523,67 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>34674</v>
+        <v>35316</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>29724</v>
+        <v>30446</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>38121</v>
+        <v>39088</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.8312744231737237</v>
+        <v>0.8338289854882479</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.7126110271353345</v>
+        <v>0.7188503032422169</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.9139026059537666</v>
+        <v>0.9228788310278616</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>36539</v>
+        <v>39324</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>32798</v>
+        <v>35639</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>38576</v>
+        <v>41389</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.9134268968360358</v>
+        <v>0.9190637115865348</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.8199195752770503</v>
+        <v>0.8329330063949594</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.9643508669466029</v>
+        <v>0.9673151862580003</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>71213</v>
+        <v>74640</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>65027</v>
+        <v>69016</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>75146</v>
+        <v>78847</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.8714906680068312</v>
+        <v>0.876663518041531</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.7957823159863116</v>
+        <v>0.8106135044576717</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.919620000954385</v>
+        <v>0.9260701943895466</v>
       </c>
     </row>
     <row r="9">
@@ -4594,16 +4594,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>41712</v>
+        <v>42354</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>41712</v>
+        <v>42354</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>41712</v>
+        <v>42354</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -4615,16 +4615,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>40002</v>
+        <v>42787</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>40002</v>
+        <v>42787</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>40002</v>
+        <v>42787</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -4636,16 +4636,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>81714</v>
+        <v>85141</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>81714</v>
+        <v>85141</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>81714</v>
+        <v>85141</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -4675,61 +4675,61 @@
         <v>6911</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>3535</v>
+        <v>3719</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>10851</v>
+        <v>11628</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.2494111935852272</v>
+        <v>0.2356929228245666</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.1275599099563548</v>
+        <v>0.1268157394918108</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.391560943324182</v>
+        <v>0.3965353236427965</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>1996</v>
+        <v>2502</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>580</v>
+        <v>883</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>5016</v>
+        <v>5874</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.1169564123209145</v>
+        <v>0.1281830106374574</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.03398767779119641</v>
+        <v>0.04522965852690099</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2939102260065496</v>
+        <v>0.3009107021091331</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>8908</v>
+        <v>9414</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>5179</v>
+        <v>5633</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>14057</v>
+        <v>14333</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.1989242997137595</v>
+        <v>0.1927256411674446</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.1156637623225022</v>
+        <v>0.1153150984715334</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.3139177217921547</v>
+        <v>0.2934391767823863</v>
       </c>
     </row>
     <row r="11">
@@ -4740,67 +4740,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>20800</v>
+        <v>22413</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>16860</v>
+        <v>17696</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>24176</v>
+        <v>25605</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.7505888064147729</v>
+        <v>0.7643070771754334</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.608439056675818</v>
+        <v>0.6034646763572036</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.8724400900436451</v>
+        <v>0.8731842605081892</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>15072</v>
+        <v>17020</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>12052</v>
+        <v>13648</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>16488</v>
+        <v>18639</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.8830435876790855</v>
+        <v>0.8718169893625425</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.7060897739934503</v>
+        <v>0.6990892978908665</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.9660123222088036</v>
+        <v>0.9547703414730986</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>35871</v>
+        <v>39432</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>30722</v>
+        <v>34513</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>39600</v>
+        <v>43213</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.8010757002862404</v>
+        <v>0.8072743588325553</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.6860822782078452</v>
+        <v>0.7065608232176142</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.8843362376774975</v>
+        <v>0.8846849015284669</v>
       </c>
     </row>
     <row r="12">
@@ -4811,16 +4811,16 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>27711</v>
+        <v>29324</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>27711</v>
+        <v>29324</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>27711</v>
+        <v>29324</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>1</v>
@@ -4832,16 +4832,16 @@
         <v>1</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>17068</v>
+        <v>19522</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>17068</v>
+        <v>19522</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>17068</v>
+        <v>19522</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>1</v>
@@ -4853,16 +4853,16 @@
         <v>1</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>44779</v>
+        <v>48846</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>44779</v>
+        <v>48846</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>44779</v>
+        <v>48846</v>
       </c>
       <c r="U12" s="6" t="n">
         <v>1</v>
@@ -4892,19 +4892,19 @@
         <v>16888</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>10971</v>
+        <v>11036</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>24746</v>
+        <v>24725</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.2114363217392745</v>
+        <v>0.199489612046059</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.1373524818121045</v>
+        <v>0.1303647460964132</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.3098079589656708</v>
+        <v>0.2920623196114355</v>
       </c>
       <c r="J13" s="5" t="n">
         <v>15</v>
@@ -4913,19 +4913,19 @@
         <v>8036</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>4807</v>
+        <v>4755</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>12970</v>
+        <v>13158</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.1073515736203532</v>
+        <v>0.1044953060025604</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.06421977594083098</v>
+        <v>0.06183104412291535</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.1732614029283338</v>
+        <v>0.1711014332410795</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>41</v>
@@ -4934,19 +4934,19 @@
         <v>24924</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>16786</v>
+        <v>17865</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>33085</v>
+        <v>33608</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.1610817151658112</v>
+        <v>0.1542724380109269</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.1084854315679945</v>
+        <v>0.110577907085279</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.2138261409371184</v>
+        <v>0.2080224123733598</v>
       </c>
     </row>
     <row r="14">
@@ -4957,67 +4957,67 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>62986</v>
+        <v>67769</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>55128</v>
+        <v>59932</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>68903</v>
+        <v>73621</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.7885636782607256</v>
+        <v>0.8005103879539411</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.6901920410343292</v>
+        <v>0.707937680388565</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.8626475181878955</v>
+        <v>0.8696352539035868</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>66820</v>
+        <v>68866</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>61886</v>
+        <v>63744</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>70049</v>
+        <v>72147</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.8926484263796467</v>
+        <v>0.8955046939974398</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.8267385970716661</v>
+        <v>0.8288985667589206</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.9357802240591688</v>
+        <v>0.9381689558770847</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>129806</v>
+        <v>136636</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>121645</v>
+        <v>127952</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>137944</v>
+        <v>143695</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.8389182848341887</v>
+        <v>0.845727561989073</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.7861738590628816</v>
+        <v>0.7919775876266404</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.8915145684320054</v>
+        <v>0.8894220929147212</v>
       </c>
     </row>
     <row r="15">
@@ -5028,16 +5028,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>79874</v>
+        <v>84657</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>79874</v>
+        <v>84657</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>79874</v>
+        <v>84657</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -5049,16 +5049,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>74856</v>
+        <v>76902</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>74856</v>
+        <v>76902</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>74856</v>
+        <v>76902</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -5070,16 +5070,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>154730</v>
+        <v>161560</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>154730</v>
+        <v>161560</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>154730</v>
+        <v>161560</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -5103,67 +5103,67 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>14429</v>
+        <v>14884</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>9697</v>
+        <v>9545</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>19963</v>
+        <v>21663</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.2713765542265071</v>
+        <v>0.2558733355679087</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.1823924001252596</v>
+        <v>0.1640910458927803</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.3754749285313597</v>
+        <v>0.372413882514494</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>7344</v>
+        <v>8736</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>3990</v>
+        <v>5067</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>12031</v>
+        <v>13770</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.2149924117468429</v>
+        <v>0.2273046233735251</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.1167992413905655</v>
+        <v>0.1318350257237182</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.3522082911957125</v>
+        <v>0.3582750492480918</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>21773</v>
+        <v>23620</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>15624</v>
+        <v>16991</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>29630</v>
+        <v>31833</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.2493212559165866</v>
+        <v>0.2445072180762874</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.178906191009674</v>
+        <v>0.1758896597406542</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.3393003346094844</v>
+        <v>0.3295311644673202</v>
       </c>
     </row>
     <row r="17">
@@ -5174,67 +5174,67 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>38739</v>
+        <v>43285</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>33205</v>
+        <v>36506</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>43471</v>
+        <v>48624</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.7286234457734929</v>
+        <v>0.7441266644320913</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.6245250714686408</v>
+        <v>0.6275861174855062</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.8176075998747405</v>
+        <v>0.8359089541072199</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>26815</v>
+        <v>29697</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>22128</v>
+        <v>24663</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>30169</v>
+        <v>33366</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.7850075882531571</v>
+        <v>0.772695376626475</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.6477917088042868</v>
+        <v>0.6417249507519082</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.8832007586094345</v>
+        <v>0.8681649742762819</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>65555</v>
+        <v>72982</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>57698</v>
+        <v>64769</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>71704</v>
+        <v>79611</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.7506787440834135</v>
+        <v>0.7554927819237128</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.6606996653905154</v>
+        <v>0.6704688355326797</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.8210938089903262</v>
+        <v>0.8241103402593453</v>
       </c>
     </row>
     <row r="18">
@@ -5245,16 +5245,16 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>53168</v>
+        <v>58169</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>53168</v>
+        <v>58169</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>53168</v>
+        <v>58169</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>1</v>
@@ -5266,16 +5266,16 @@
         <v>1</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>34159</v>
+        <v>38433</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>34159</v>
+        <v>38433</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>34159</v>
+        <v>38433</v>
       </c>
       <c r="N18" s="6" t="n">
         <v>1</v>
@@ -5287,16 +5287,16 @@
         <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>87328</v>
+        <v>96602</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>87328</v>
+        <v>96602</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>87328</v>
+        <v>96602</v>
       </c>
       <c r="U18" s="6" t="n">
         <v>1</v>
@@ -5537,67 +5537,67 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>56468</v>
+        <v>56923</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>46497</v>
+        <v>46635</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>68939</v>
+        <v>70194</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.1948085260965677</v>
+        <v>0.1869568303792374</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.1604085492871668</v>
+        <v>0.1531667703267386</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.2378314114666072</v>
+        <v>0.2305415822540822</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>27237</v>
+        <v>29135</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>20238</v>
+        <v>22161</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>35716</v>
+        <v>37675</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.1169186301903563</v>
+        <v>0.1187350077033143</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.08687525395291937</v>
+        <v>0.09031329681590375</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.1533162025133784</v>
+        <v>0.15353739450664</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="R22" s="5" t="n">
-        <v>83705</v>
+        <v>86059</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>70231</v>
+        <v>72503</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>98699</v>
+        <v>100630</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.1601025912962567</v>
+        <v>0.1565117931648985</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.1343305021466333</v>
+        <v>0.1318583251594932</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.188781206125937</v>
+        <v>0.1830115374881159</v>
       </c>
     </row>
     <row r="23">
@@ -5608,67 +5608,67 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>317</v>
+        <v>336</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>233397</v>
+        <v>247551</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>220926</v>
+        <v>234280</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>243368</v>
+        <v>257839</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.8051914739034323</v>
+        <v>0.8130431696207626</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.7621685885333926</v>
+        <v>0.7694584177459177</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.8395914507128331</v>
+        <v>0.8468332296732612</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>205721</v>
+        <v>216246</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>197242</v>
+        <v>207706</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>212720</v>
+        <v>223220</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.8830813698096436</v>
+        <v>0.8812649922966856</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.8466837974866217</v>
+        <v>0.8464626054933601</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.9131247460470808</v>
+        <v>0.9096867031840963</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>623</v>
+        <v>658</v>
       </c>
       <c r="R23" s="5" t="n">
-        <v>439118</v>
+        <v>463796</v>
       </c>
       <c r="S23" s="5" t="n">
-        <v>424124</v>
+        <v>449225</v>
       </c>
       <c r="T23" s="5" t="n">
-        <v>452592</v>
+        <v>477352</v>
       </c>
       <c r="U23" s="6" t="n">
-        <v>0.8398974087037433</v>
+        <v>0.8434882068351015</v>
       </c>
       <c r="V23" s="6" t="n">
-        <v>0.8112187938740635</v>
+        <v>0.8169884625118841</v>
       </c>
       <c r="W23" s="6" t="n">
-        <v>0.8656694978533668</v>
+        <v>0.8681416748405069</v>
       </c>
     </row>
     <row r="24">
@@ -5679,16 +5679,16 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>289865</v>
+        <v>304474</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>289865</v>
+        <v>304474</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>289865</v>
+        <v>304474</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>1</v>
@@ -5700,16 +5700,16 @@
         <v>1</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>352</v>
+        <v>371</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>232958</v>
+        <v>245381</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>232958</v>
+        <v>245381</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>232958</v>
+        <v>245381</v>
       </c>
       <c r="N24" s="6" t="n">
         <v>1</v>
@@ -5721,16 +5721,16 @@
         <v>1</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>753</v>
+        <v>792</v>
       </c>
       <c r="R24" s="5" t="n">
-        <v>522823</v>
+        <v>549855</v>
       </c>
       <c r="S24" s="5" t="n">
-        <v>522823</v>
+        <v>549855</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>522823</v>
+        <v>549855</v>
       </c>
       <c r="U24" s="6" t="n">
         <v>1</v>
